--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_20_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_20_same_sheet.xlsx
@@ -416,7 +416,7 @@
         <v>1.53430814688792</v>
       </c>
       <c r="E6" t="n">
-        <v>0.202</v>
+        <v>0.205</v>
       </c>
     </row>
     <row r="7">
@@ -481,7 +481,7 @@
         <v>2.28321246214754</v>
       </c>
       <c r="E12" t="n">
-        <v>0.142</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="13">

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_20_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_20_same_sheet.xlsx
@@ -416,7 +416,7 @@
         <v>1.53430814688792</v>
       </c>
       <c r="E6" t="n">
-        <v>0.205</v>
+        <v>0.211</v>
       </c>
     </row>
     <row r="7">
@@ -481,7 +481,7 @@
         <v>2.28321246214754</v>
       </c>
       <c r="E12" t="n">
-        <v>0.132</v>
+        <v>0.143</v>
       </c>
     </row>
     <row r="13">
@@ -546,7 +546,7 @@
         <v>0.719885999574792</v>
       </c>
       <c r="E18" t="n">
-        <v>0.411</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="19">

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_20_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_20_same_sheet.xlsx
@@ -416,7 +416,7 @@
         <v>1.53430814688792</v>
       </c>
       <c r="E6" t="n">
-        <v>0.211</v>
+        <v>0.201</v>
       </c>
     </row>
     <row r="7">
@@ -481,7 +481,7 @@
         <v>2.28321246214754</v>
       </c>
       <c r="E12" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="13">
@@ -546,7 +546,7 @@
         <v>0.719885999574792</v>
       </c>
       <c r="E18" t="n">
-        <v>0.43</v>
+        <v>0.463</v>
       </c>
     </row>
     <row r="19">

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_20_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_20_same_sheet.xlsx
@@ -407,16 +407,16 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0846244098603759</v>
+        <v>0.0901300077826431</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0322779105598148</v>
+        <v>0.0358474328410811</v>
       </c>
       <c r="D6" t="n">
-        <v>1.53430814688792</v>
+        <v>1.71029146927317</v>
       </c>
       <c r="E6" t="n">
-        <v>0.201</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="7">
@@ -424,10 +424,10 @@
         <v>46</v>
       </c>
       <c r="B7" t="n">
-        <v>2.53711932734829</v>
+        <v>2.42413672317708</v>
       </c>
       <c r="C7" t="n">
-        <v>0.967722089440185</v>
+        <v>0.964152567158919</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -437,7 +437,7 @@
         <v>47</v>
       </c>
       <c r="B8" t="n">
-        <v>2.62174373720867</v>
+        <v>2.51426673095972</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -481,7 +481,7 @@
         <v>2.28321246214754</v>
       </c>
       <c r="E12" t="n">
-        <v>0.142</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="13">
@@ -537,16 +537,16 @@
         <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0684203461803049</v>
+        <v>0.0686972056212772</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0154085564245885</v>
+        <v>0.015873812596781</v>
       </c>
       <c r="D18" t="n">
-        <v>0.719885999574792</v>
+        <v>0.741973324964217</v>
       </c>
       <c r="E18" t="n">
-        <v>0.463</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="19">
@@ -554,10 +554,10 @@
         <v>46</v>
       </c>
       <c r="B19" t="n">
-        <v>4.37199212952194</v>
+        <v>4.25900952535073</v>
       </c>
       <c r="C19" t="n">
-        <v>0.984591443575411</v>
+        <v>0.984126187403219</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -567,7 +567,7 @@
         <v>47</v>
       </c>
       <c r="B20" t="n">
-        <v>4.44041247570225</v>
+        <v>4.327706730972</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_20_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_20_same_sheet.xlsx
@@ -416,7 +416,7 @@
         <v>1.71029146927317</v>
       </c>
       <c r="E6" t="n">
-        <v>0.162</v>
+        <v>0.189</v>
       </c>
     </row>
     <row r="7">
@@ -481,7 +481,7 @@
         <v>2.28321246214754</v>
       </c>
       <c r="E12" t="n">
-        <v>0.14</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="13">
@@ -546,7 +546,7 @@
         <v>0.741973324964217</v>
       </c>
       <c r="E18" t="n">
-        <v>0.448</v>
+        <v>0.441</v>
       </c>
     </row>
     <row r="19">
